--- a/data/2025/35-suceava/146263-suceava/budget_file.xlsx
+++ b/data/2025/35-suceava/146263-suceava/budget_file.xlsx
@@ -873,64 +873,76 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>07.02.01</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>A3. IMPOZITE SI TAXE PE PROPRIETATE</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>63396740</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
+      <c r="G14" s="5" t="n">
+        <v>75691490</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>07.02.01 total: parent 75.691.490,00 != sum(children) 63.396.740,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>07.02</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Impozite si taxe pe proprietate</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="5" t="n">
         <v>75691490</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>07.02 total: parent 75.691.490,00 != sum(children) 87.986.240,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -2738,11 +2750,11 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>63396740</v>
+        <v>75691490</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -2752,33 +2764,39 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>07.02</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Impozite si taxe pe proprietate</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>849</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="5" t="n">
         <v>75691490</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>07.02 total: parent 75.691.490,00 != sum(children) 87.986.240,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -4622,44 +4640,50 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4000</v>
+        <v>374000</v>
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>39.02</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Venituri din valorificarea unor bunuri</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>374000</v>
       </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>39.02 total: parent 374.000,00 != sum(children) 744.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -10404,36 +10428,42 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="B177" s="4" t="n"/>
+      <c r="C177" s="4" t="inlineStr">
         <is>
           <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
-      <c r="D177" t="n">
+      <c r="D177" s="4" t="n">
         <v>231</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E177" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F177" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G177" s="3" t="n">
+      <c r="G177" s="5" t="n">
         <v>37808660</v>
       </c>
-      <c r="H177" s="3" t="n">
+      <c r="H177" s="5" t="n">
         <v>362827</v>
       </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>51.02 total: parent 37.808.660,00 != sum(children) 1.066.600,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -14165,36 +14195,42 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="A276" s="4" t="inlineStr">
         <is>
           <t>61.02</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="B276" s="4" t="n"/>
+      <c r="C276" s="4" t="inlineStr">
         <is>
           <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
-      <c r="D276" t="n">
+      <c r="D276" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="E276" t="n">
+      <c r="E276" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F276" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G276" s="3" t="n">
+      <c r="G276" s="5" t="n">
         <v>15621620</v>
       </c>
-      <c r="H276" s="3" t="n">
+      <c r="H276" s="5" t="n">
         <v>297387</v>
       </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I276" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>61.02 total: parent 15.621.620,00 != sum(children) 258.600,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -16210,36 +16246,42 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
+      <c r="A330" s="4" t="inlineStr">
         <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="B330" s="4" t="n"/>
+      <c r="C330" s="4" t="inlineStr">
         <is>
           <t>Invatamant</t>
         </is>
       </c>
-      <c r="D330" t="n">
+      <c r="D330" s="4" t="n">
         <v>384</v>
       </c>
-      <c r="E330" t="n">
+      <c r="E330" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F330" t="inlineStr">
+      <c r="F330" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G330" s="3" t="n">
+      <c r="G330" s="5" t="n">
         <v>185172330</v>
       </c>
-      <c r="H330" s="3" t="n">
+      <c r="H330" s="5" t="n">
         <v>4726857</v>
       </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I330" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J330" s="4" t="inlineStr">
+        <is>
+          <t>65.02 total: parent 185.172.330,00 != sum(children) 7.335.100,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20446,36 +20488,42 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr">
+      <c r="A441" s="4" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
+      <c r="B441" s="4" t="n"/>
+      <c r="C441" s="4" t="inlineStr">
         <is>
           <t>Cultura, recreere si religie</t>
         </is>
       </c>
-      <c r="D441" t="n">
+      <c r="D441" s="4" t="n">
         <v>495</v>
       </c>
-      <c r="E441" t="n">
+      <c r="E441" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F441" t="inlineStr">
+      <c r="F441" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G441" s="3" t="n">
+      <c r="G441" s="5" t="n">
         <v>47939000</v>
       </c>
-      <c r="H441" s="3" t="n">
+      <c r="H441" s="5" t="n">
         <v>3179059</v>
       </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I441" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J441" s="4" t="inlineStr">
+        <is>
+          <t>67.02 total: parent 47.939.000,00 != sum(children) 4.016.990,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -20900,41 +20948,46 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
+      <c r="A453" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
+      <c r="B453" s="4" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr">
+      <c r="C453" s="4" t="inlineStr">
         <is>
           <t>TITLUL II BUNURI SI SERVICII</t>
         </is>
       </c>
-      <c r="D453" t="n">
+      <c r="D453" s="4" t="n">
         <v>507</v>
       </c>
-      <c r="E453" t="n">
+      <c r="E453" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G453" s="3" t="n">
+      <c r="F453" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G453" s="5" t="n">
         <v>17281600</v>
       </c>
-      <c r="H453" s="3" t="n">
+      <c r="H453" s="5" t="n">
         <v>3133730</v>
       </c>
-      <c r="I453" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I453" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J453" s="4" t="inlineStr">
+        <is>
+          <t>20 total: parent 17.281.600,00 != sum(children) 17.280.706,00 (8 children); 20 credite_restante: parent 3.133.730,00 != sum(children) 3.112.976,00 (8 children)</t>
         </is>
       </c>
     </row>
@@ -21356,14 +21409,14 @@
         </is>
       </c>
       <c r="G464" s="3" t="n">
-        <v>900</v>
+        <v>6</v>
       </c>
       <c r="H464" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -21553,12 +21606,10 @@
       <c r="G469" s="3" t="n">
         <v>110000</v>
       </c>
-      <c r="H469" s="3" t="n">
-        <v>750</v>
-      </c>
+      <c r="H469" s="3" t="n"/>
       <c r="I469" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -21666,12 +21717,10 @@
       <c r="G472" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="H472" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="H472" s="3" t="n"/>
       <c r="I472" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -21705,12 +21754,10 @@
       <c r="G473" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="H473" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="H473" s="3" t="n"/>
       <c r="I473" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -21744,12 +21791,10 @@
       <c r="G474" s="3" t="n">
         <v>798740</v>
       </c>
-      <c r="H474" s="3" t="n">
-        <v>20004</v>
-      </c>
+      <c r="H474" s="3" t="n"/>
       <c r="I474" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -23640,36 +23685,42 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
+      <c r="A526" s="4" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
+      <c r="B526" s="4" t="n"/>
+      <c r="C526" s="4" t="inlineStr">
         <is>
           <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
-      <c r="D526" t="n">
+      <c r="D526" s="4" t="n">
         <v>580</v>
       </c>
-      <c r="E526" t="n">
+      <c r="E526" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F526" t="inlineStr">
+      <c r="F526" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G526" s="3" t="n">
+      <c r="G526" s="5" t="n">
         <v>49971120</v>
       </c>
-      <c r="H526" s="3" t="n">
+      <c r="H526" s="5" t="n">
         <v>467978</v>
       </c>
-      <c r="I526" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I526" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J526" s="4" t="inlineStr">
+        <is>
+          <t>68.02 total: parent 49.971.120,00 != sum(children) -100,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -25733,36 +25784,42 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
+      <c r="A582" s="4" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="B582" s="4" t="n"/>
+      <c r="C582" s="4" t="inlineStr">
         <is>
           <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
-      <c r="D582" t="n">
+      <c r="D582" s="4" t="n">
         <v>636</v>
       </c>
-      <c r="E582" t="n">
+      <c r="E582" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="F582" t="inlineStr">
+      <c r="F582" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G582" s="3" t="n">
+      <c r="G582" s="5" t="n">
         <v>122525170</v>
       </c>
-      <c r="H582" s="3" t="n">
+      <c r="H582" s="5" t="n">
         <v>3528873</v>
       </c>
-      <c r="I582" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I582" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J582" s="4" t="inlineStr">
+        <is>
+          <t>70.02 total: parent 122.525.170,00 != sum(children) 22.806.790,00 (2 children); 70.02 credite_restante: parent 3.528.873,00 != sum(children) 48.475,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -27806,36 +27863,42 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr">
+      <c r="A637" s="4" t="inlineStr">
         <is>
           <t>74.02</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
+      <c r="B637" s="4" t="n"/>
+      <c r="C637" s="4" t="inlineStr">
         <is>
           <t>Protectia mediului</t>
         </is>
       </c>
-      <c r="D637" t="n">
+      <c r="D637" s="4" t="n">
         <v>691</v>
       </c>
-      <c r="E637" t="n">
+      <c r="E637" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="F637" t="inlineStr">
+      <c r="F637" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G637" s="3" t="n">
+      <c r="G637" s="5" t="n">
         <v>70493000</v>
       </c>
-      <c r="H637" s="3" t="n">
+      <c r="H637" s="5" t="n">
         <v>940895</v>
       </c>
-      <c r="I637" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I637" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J637" s="4" t="inlineStr">
+        <is>
+          <t>74.02 total: parent 70.493.000,00 != sum(children) 1.000.300,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -29708,36 +29771,42 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr">
+      <c r="A687" s="4" t="inlineStr">
         <is>
           <t>80.02</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr">
+      <c r="B687" s="4" t="n"/>
+      <c r="C687" s="4" t="inlineStr">
         <is>
           <t>Actiuni generale economice, comerciale si de munca</t>
         </is>
       </c>
-      <c r="D687" t="n">
+      <c r="D687" s="4" t="n">
         <v>741</v>
       </c>
-      <c r="E687" t="n">
+      <c r="E687" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F687" t="inlineStr">
+      <c r="F687" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G687" s="3" t="n">
+      <c r="G687" s="5" t="n">
         <v>4991010</v>
       </c>
-      <c r="H687" s="3" t="n">
+      <c r="H687" s="5" t="n">
         <v>1440033</v>
       </c>
-      <c r="I687" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I687" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J687" s="4" t="inlineStr">
+        <is>
+          <t>80.02 total: parent 4.991.010,00 != sum(children) 70.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -30425,36 +30494,42 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" t="inlineStr">
+      <c r="A706" s="4" t="inlineStr">
         <is>
           <t>81.02</t>
         </is>
       </c>
-      <c r="C706" t="inlineStr">
+      <c r="B706" s="4" t="n"/>
+      <c r="C706" s="4" t="inlineStr">
         <is>
           <t>Combustibili si energie</t>
         </is>
       </c>
-      <c r="D706" t="n">
+      <c r="D706" s="4" t="n">
         <v>760</v>
       </c>
-      <c r="E706" t="n">
+      <c r="E706" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="F706" t="inlineStr">
+      <c r="F706" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G706" s="3" t="n">
+      <c r="G706" s="5" t="n">
         <v>25491280</v>
       </c>
-      <c r="H706" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I706" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H706" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I706" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J706" s="4" t="inlineStr">
+        <is>
+          <t>81.02 total: parent 25.491.280,00 != sum(children) 6.780.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -31334,36 +31409,42 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" t="inlineStr">
+      <c r="A730" s="4" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr">
+      <c r="B730" s="4" t="n"/>
+      <c r="C730" s="4" t="inlineStr">
         <is>
           <t>Transporturi</t>
         </is>
       </c>
-      <c r="D730" t="n">
+      <c r="D730" s="4" t="n">
         <v>784</v>
       </c>
-      <c r="E730" t="n">
+      <c r="E730" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="F730" t="inlineStr">
+      <c r="F730" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G730" s="3" t="n">
+      <c r="G730" s="5" t="n">
         <v>184372730</v>
       </c>
-      <c r="H730" s="3" t="n">
+      <c r="H730" s="5" t="n">
         <v>1701620</v>
       </c>
-      <c r="I730" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I730" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J730" s="4" t="inlineStr">
+        <is>
+          <t>84.02 total: parent 184.372.730,00 != sum(children) 24.412.800,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -58740,36 +58821,42 @@
       </c>
     </row>
     <row r="1449">
-      <c r="A1449" t="inlineStr">
+      <c r="A1449" s="4" t="inlineStr">
         <is>
           <t>65.02</t>
         </is>
       </c>
-      <c r="C1449" t="inlineStr">
+      <c r="B1449" s="4" t="n"/>
+      <c r="C1449" s="4" t="inlineStr">
         <is>
           <t>Invatamant</t>
         </is>
       </c>
-      <c r="D1449" t="n">
+      <c r="D1449" s="4" t="n">
         <v>1566</v>
       </c>
-      <c r="E1449" t="n">
+      <c r="E1449" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="F1449" t="inlineStr">
+      <c r="F1449" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1449" s="3" t="n">
+      <c r="G1449" s="5" t="n">
         <v>122353330</v>
       </c>
-      <c r="H1449" s="3" t="n">
+      <c r="H1449" s="5" t="n">
         <v>2490947</v>
       </c>
-      <c r="I1449" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1449" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J1449" s="4" t="inlineStr">
+        <is>
+          <t>65.02 total: parent 122.353.330,00 != sum(children) 7.335.100,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -60100,36 +60187,42 @@
       </c>
     </row>
     <row r="1485">
-      <c r="A1485" t="inlineStr">
+      <c r="A1485" s="4" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="C1485" t="inlineStr">
+      <c r="B1485" s="4" t="n"/>
+      <c r="C1485" s="4" t="inlineStr">
         <is>
           <t>Cultura, recreere si religie</t>
         </is>
       </c>
-      <c r="D1485" t="n">
+      <c r="D1485" s="4" t="n">
         <v>1602</v>
       </c>
-      <c r="E1485" t="n">
+      <c r="E1485" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="F1485" t="inlineStr">
+      <c r="F1485" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1485" s="3" t="n">
+      <c r="G1485" s="5" t="n">
         <v>6391080</v>
       </c>
-      <c r="H1485" s="3" t="n">
+      <c r="H1485" s="5" t="n">
         <v>16374</v>
       </c>
-      <c r="I1485" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1485" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J1485" s="4" t="inlineStr">
+        <is>
+          <t>67.02 total: parent 6.391.080,00 != sum(children) 2.659.190,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -61534,36 +61627,42 @@
       </c>
     </row>
     <row r="1523">
-      <c r="A1523" t="inlineStr">
+      <c r="A1523" s="4" t="inlineStr">
         <is>
           <t>70.02</t>
         </is>
       </c>
-      <c r="C1523" t="inlineStr">
+      <c r="B1523" s="4" t="n"/>
+      <c r="C1523" s="4" t="inlineStr">
         <is>
           <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
-      <c r="D1523" t="n">
+      <c r="D1523" s="4" t="n">
         <v>1640</v>
       </c>
-      <c r="E1523" t="n">
+      <c r="E1523" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="F1523" t="inlineStr">
+      <c r="F1523" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1523" s="3" t="n">
+      <c r="G1523" s="5" t="n">
         <v>91968070</v>
       </c>
-      <c r="H1523" s="3" t="n">
+      <c r="H1523" s="5" t="n">
         <v>356606</v>
       </c>
-      <c r="I1523" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1523" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J1523" s="4" t="inlineStr">
+        <is>
+          <t>70.02 total: parent 91.968.070,00 != sum(children) 22.810.190,00 (1 children); 70.02 credite_restante: parent 356.606,00 != sum(children) 48.475,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -62197,36 +62296,42 @@
       </c>
     </row>
     <row r="1541">
-      <c r="A1541" t="inlineStr">
+      <c r="A1541" s="4" t="inlineStr">
         <is>
           <t>74.02</t>
         </is>
       </c>
-      <c r="C1541" t="inlineStr">
+      <c r="B1541" s="4" t="n"/>
+      <c r="C1541" s="4" t="inlineStr">
         <is>
           <t>Protectia mediului</t>
         </is>
       </c>
-      <c r="D1541" t="n">
+      <c r="D1541" s="4" t="n">
         <v>1658</v>
       </c>
-      <c r="E1541" t="n">
+      <c r="E1541" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="F1541" t="inlineStr">
+      <c r="F1541" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1541" s="3" t="n">
+      <c r="G1541" s="5" t="n">
         <v>21697750</v>
       </c>
-      <c r="H1541" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1541" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H1541" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1541" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J1541" s="4" t="inlineStr">
+        <is>
+          <t>74.02 total: parent 21.697.750,00 != sum(children) 1.002.500,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63138,36 +63243,42 @@
       </c>
     </row>
     <row r="1566">
-      <c r="A1566" t="inlineStr">
+      <c r="A1566" s="4" t="inlineStr">
         <is>
           <t>80.02</t>
         </is>
       </c>
-      <c r="C1566" t="inlineStr">
+      <c r="B1566" s="4" t="n"/>
+      <c r="C1566" s="4" t="inlineStr">
         <is>
           <t>Actiuni generale economice, comerciale si de munca</t>
         </is>
       </c>
-      <c r="D1566" t="n">
+      <c r="D1566" s="4" t="n">
         <v>1683</v>
       </c>
-      <c r="E1566" t="n">
+      <c r="E1566" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="F1566" t="inlineStr">
+      <c r="F1566" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1566" s="3" t="n">
+      <c r="G1566" s="5" t="n">
         <v>4991010</v>
       </c>
-      <c r="H1566" s="3" t="n">
+      <c r="H1566" s="5" t="n">
         <v>1440033</v>
       </c>
-      <c r="I1566" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1566" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J1566" s="4" t="inlineStr">
+        <is>
+          <t>80.02 total: parent 4.991.010,00 != sum(children) 70.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -63865,36 +63976,42 @@
       </c>
     </row>
     <row r="1585">
-      <c r="A1585" t="inlineStr">
+      <c r="A1585" s="4" t="inlineStr">
         <is>
           <t>81.02</t>
         </is>
       </c>
-      <c r="C1585" t="inlineStr">
+      <c r="B1585" s="4" t="n"/>
+      <c r="C1585" s="4" t="inlineStr">
         <is>
           <t>Combustibili si energie</t>
         </is>
       </c>
-      <c r="D1585" t="n">
+      <c r="D1585" s="4" t="n">
         <v>1702</v>
       </c>
-      <c r="E1585" t="n">
+      <c r="E1585" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="F1585" t="inlineStr">
+      <c r="F1585" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1585" s="3" t="n">
+      <c r="G1585" s="5" t="n">
         <v>969060</v>
       </c>
-      <c r="H1585" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1585" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H1585" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1585" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J1585" s="4" t="inlineStr">
+        <is>
+          <t>81.02 total: parent 969.060,00 != sum(children) 950.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -64285,36 +64402,42 @@
       </c>
     </row>
     <row r="1596">
-      <c r="A1596" t="inlineStr">
+      <c r="A1596" s="4" t="inlineStr">
         <is>
           <t>84.02</t>
         </is>
       </c>
-      <c r="C1596" t="inlineStr">
+      <c r="B1596" s="4" t="n"/>
+      <c r="C1596" s="4" t="inlineStr">
         <is>
           <t>Transporturi</t>
         </is>
       </c>
-      <c r="D1596" t="n">
+      <c r="D1596" s="4" t="n">
         <v>1713</v>
       </c>
-      <c r="E1596" t="n">
+      <c r="E1596" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="F1596" t="inlineStr">
+      <c r="F1596" s="4" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G1596" s="3" t="n">
+      <c r="G1596" s="5" t="n">
         <v>116827600</v>
       </c>
-      <c r="H1596" s="3" t="n">
+      <c r="H1596" s="5" t="n">
         <v>169459</v>
       </c>
-      <c r="I1596" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="I1596" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="J1596" s="4" t="inlineStr">
+        <is>
+          <t>84.02 total: parent 116.827.600,00 != sum(children) 8.908.800,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65556,7 +65679,7 @@
       </c>
       <c r="J1629" s="4" t="inlineStr">
         <is>
-          <t>99.02 credite_restante: parent 0,00 != sum(children) 48.475,00 (1 children); 99.02 total: parent 2.600.000,00 != sum(children) 45.339.980,00 (1 children)</t>
+          <t>99.02 total: parent 2.600.000,00 != sum(children) 45.339.980,00 (1 children); 99.02 credite_restante: parent 0,00 != sum(children) 48.475,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -65571,7 +65694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F171"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -65617,12 +65740,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -65630,29 +65753,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>07.02.01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 07.02.01 total: sum now consistent — applied</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -65660,7 +65778,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>07.02.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -65670,27 +65788,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 total: sum now consistent — applied</t>
+          <t>07.02.01 total: parent 75.691.490,00 != sum(children) 63.396.740,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>07.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -65700,14 +65818,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>07.02 total: parent 75.691.490,00 != sum(children) 87.986.240,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -65716,71 +65834,61 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>07.02.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p1 with different values</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 39.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -65790,87 +65898,77 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 11 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>11.02 total: parent 89.011.000,00 != sum(children) 230.038.280,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 51.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 61.02 total: sum now consistent — applied</t>
+          <t>code 30.00.02 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -65880,207 +65978,187 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 7 rows for 65.02 total: sum now consistent — applied</t>
+          <t>30.02 total: parent 21.489.170,00 != sum(children) 83.094.960,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 67.02 total: sum now consistent — applied</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 20 credite_restante: sum now consistent — applied</t>
+          <t>39.02 total: parent 374.000,00 != sum(children) 744.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>39.02.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LLM re-read 9 rows for 20 total: sum now consistent — applied</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 68.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 70.02 credite_restante: sum now consistent — applied</t>
+          <t>42.02 total: parent 177.986.180,00 != sum(children) 387.731.900,00 (10 children)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 70.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (36%): 'Ssuen sa sae u   ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -66090,27 +66168,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 74.02 total: sum now consistent — applied</t>
+          <t>51.02 total: parent 37.808.660,00 != sum(children) 1.066.600,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -66120,27 +66198,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 81 total: still inconsistent — UNRESOLVED</t>
+          <t>61.02 total: parent 15.621.620,00 != sum(children) 258.600,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -66150,27 +66228,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 total: sum now consistent — applied</t>
+          <t>65.02 total: parent 185.172.330,00 != sum(children) 7.335.100,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -66180,27 +66258,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 81.02 total: sum now consistent — applied</t>
+          <t>67.02 total: parent 47.939.000,00 != sum(children) 4.016.990,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -66210,57 +66288,57 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total: sum now consistent — applied</t>
+          <t>20 total: parent 17.281.600,00 != sum(children) 17.280.706,00 (8 children)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>07.02.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 07.02.01 total: still inconsistent — UNRESOLVED</t>
+          <t>20 credite_restante: parent 3.133.730,00 != sum(children) 3.112.976,00 (8 children)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>07.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -66270,27 +66348,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 07.02 total: sum now consistent — applied</t>
+          <t>68.02 total: parent 49.971.120,00 != sum(children) -100,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -66300,57 +66378,57 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>70.02 total: parent 122.525.170,00 != sum(children) 22.806.790,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>70.02 credite_restante: parent 3.528.873,00 != sum(children) 48.475,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -66360,57 +66438,52 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>74.02 total: parent 70.493.000,00 != sum(children) 1.000.300,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 65.02 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (36%): 'Suenn  u ud us  ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -66420,57 +66493,57 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 67.02 total: sum now consistent — applied</t>
+          <t>81 total: parent 2.320.000,00 != sum(children) 3.680.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 70.02 credite_restante: sum now consistent — applied</t>
+          <t>80.02 total: parent 4.991.010,00 != sum(children) 70.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -66480,27 +66553,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 70.02 total: sum now consistent — applied</t>
+          <t>81.02 total: parent 25.491.280,00 != sum(children) 6.780.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -66510,57 +66583,52 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 74.02 total: sum now consistent — applied</t>
+          <t>84.02 total: parent 184.372.730,00 != sum(children) 24.412.800,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>80.02</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 80.02 total: sum now consistent — applied</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>07.02.01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -66570,27 +66638,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 81.02 total: sum now consistent — applied</t>
+          <t>07.02.01 total: parent 75.691.490,00 != sum(children) 63.396.740,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>07.02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -66600,39 +66668,39 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total: sum now consistent — applied</t>
+          <t>07.02 total: parent 75.691.490,00 != sum(children) 87.986.240,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>07.02.01</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>duplicate of p35 with different values</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -66641,103 +66709,103 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>07.02.01</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>duplicate of p1 with different values</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>11.02 total: parent 89.011.000,00 != sum(children) 230.038.280,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>11.02 total: parent 89.011.000,00 != sum(children) 230.038.280,00 (4 children)</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>code 30.00.02 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -66746,23 +66814,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>30.00.02</t>
+          <t>30.02</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>code 30.00.02 (revenue) not in nomenclator</t>
+          <t>30.02 total: parent 21.489.170,00 != sum(children) 29.834.880,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -66771,71 +66844,71 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>30.02 total: parent 21.489.170,00 != sum(children) 83.094.960,00 (3 children)</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>39.02.01</t>
+          <t>42.02</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>42.02 total: parent 7.294.560,00 != sum(children) 14.749.120,00 (4 children)</t>
         </is>
       </c>
     </row>
@@ -66851,53 +66924,48 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>name mismatch vs nomenclator (36%): 'Suenn sn e u s  ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>42.02 total: parent 177.986.180,00 != sum(children) 387.731.900,00 (10 children)</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -66906,23 +66974,23 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>55.01.84</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Ssuen sa sae u   ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -66931,101 +66999,91 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>55.01.84</t>
+          <t>20.05.01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Suenn  u ud us  ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>20.05.30</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>81 total: parent 2.320.000,00 != sum(children) 3.680.000,00 (2 children)</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>07.02.01</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>20.06.01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>07.02.01 total: parent 75.691.490,00 != sum(children) 63.396.740,00 (2 children)</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -67041,23 +67099,23 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>07.02.01</t>
+          <t>20.06.02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>duplicate of p35 with different values</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -67066,53 +67124,48 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>11.02 total: parent 89.011.000,00 != sum(children) 230.038.280,00 (4 children)</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -67121,103 +67174,98 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>30.00.02</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>code 30.00.02 (revenue) not in nomenclator</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>30.02 total: parent 21.489.170,00 != sum(children) 29.834.880,00 (3 children)</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>20.30.01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -67226,53 +67274,48 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>20.30.02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>20.30.03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>42.02 total: parent 7.294.560,00 != sum(children) 14.749.120,00 (4 children)</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -67281,16 +67324,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>55.01.84</t>
+          <t>20.30.30</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Suenn sn e u s  ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67306,16 +67349,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67331,16 +67374,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67360,12 +67403,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20.05.01</t>
+          <t>59.40</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67385,12 +67428,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20.05.30</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67410,12 +67453,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>85.01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67435,12 +67478,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20.06.01</t>
+          <t>51.02.01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67460,12 +67503,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20.06.02</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67485,12 +67528,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -67506,16 +67549,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p14 with different values</t>
         </is>
       </c>
     </row>
@@ -67531,16 +67574,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p14 with different values</t>
         </is>
       </c>
     </row>
@@ -67556,16 +67599,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>61.02.03</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -67581,16 +67624,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>61.02.03.04</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -67606,16 +67649,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20.30.01</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -67631,16 +67674,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20.30.02</t>
+          <t>65.02.03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -67656,16 +67699,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20.30.03</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -67681,16 +67724,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20.30.30</t>
+          <t>65.02.04</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -67706,16 +67749,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>65.02.04.01</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -67731,16 +67774,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -67756,16 +67799,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>59.40</t>
+          <t>65.02.04.03</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -67781,16 +67824,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>65.02.13</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -67806,16 +67849,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p20 with different values</t>
         </is>
       </c>
     </row>
@@ -67831,16 +67874,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>51.02.01</t>
+          <t>20.04.02</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p21 with different values</t>
         </is>
       </c>
     </row>
@@ -67856,16 +67899,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -67881,16 +67924,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>20.06.01</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -67906,16 +67949,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>20.06.02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>duplicate of p14 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -67931,16 +67974,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>duplicate of p14 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -67956,16 +67999,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>61.02.03</t>
+          <t>20.14</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -67981,16 +68024,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>61.02.03.04</t>
+          <t>20.30</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68006,16 +68049,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>20.30.03</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68031,16 +68074,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>65.02.03</t>
+          <t>20.30.30</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68056,16 +68099,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68081,16 +68124,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>65.02.04</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68106,16 +68149,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>65.02.04.01</t>
+          <t>51.01.01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68131,16 +68174,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68156,16 +68199,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>65.02.04.03</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68181,16 +68224,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>65.02.13</t>
+          <t>55.01.18</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>duplicate of p19 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68206,16 +68249,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>duplicate of p20 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68231,16 +68274,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20.04.02</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>duplicate of p21 with different values</t>
+          <t>duplicate of p22 with different values</t>
         </is>
       </c>
     </row>
@@ -68256,11 +68299,11 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>57.02.01</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -68281,11 +68324,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20.06.01</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -68306,11 +68349,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20.06.02</t>
+          <t>59.08</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -68331,11 +68374,11 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -68356,11 +68399,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>59.40</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -68381,11 +68424,11 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>59.44</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -68397,7 +68440,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -68406,16 +68449,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20.30.03</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>name mismatch vs nomenclator (36%): 'OPERATIUNI FINANCIARE' vs 'Protectia mediului'</t>
         </is>
       </c>
     </row>
@@ -68435,12 +68478,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20.30.30</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p28 with different values</t>
         </is>
       </c>
     </row>
@@ -68460,12 +68503,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p30 with different values</t>
         </is>
       </c>
     </row>
@@ -68485,12 +68528,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>67.02.03</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p23 with different values</t>
         </is>
       </c>
     </row>
@@ -68510,12 +68553,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>51.01.01</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p23 with different values</t>
         </is>
       </c>
     </row>
@@ -68531,16 +68574,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>67.02.03.30</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -68556,16 +68599,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>55.01</t>
+          <t>67.02.05</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -68581,16 +68624,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>55.01.18</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -68606,16 +68649,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p24 with different values</t>
         </is>
       </c>
     </row>
@@ -68631,16 +68674,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p25 with different values</t>
         </is>
       </c>
     </row>
@@ -68656,16 +68699,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>57.02.01</t>
+          <t>68.02.15</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p26 with different values</t>
         </is>
       </c>
     </row>
@@ -68681,16 +68724,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>68.02.15.02</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p26 with different values</t>
         </is>
       </c>
     </row>
@@ -68706,16 +68749,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>59.08</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p26 with different values</t>
         </is>
       </c>
     </row>
@@ -68731,16 +68774,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>70.02.06</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p28 with different values</t>
         </is>
       </c>
     </row>
@@ -68756,16 +68799,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>59.40</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p28 with different values</t>
         </is>
       </c>
     </row>
@@ -68781,23 +68824,23 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>59.44</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>duplicate of p22 with different values</t>
+          <t>duplicate of p28 with different values</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -68806,16 +68849,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>20.05.30</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'OPERATIUNI FINANCIARE' vs 'Protectia mediului'</t>
+          <t>duplicate of p29 with different values</t>
         </is>
       </c>
     </row>
@@ -68831,16 +68874,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>duplicate of p28 with different values</t>
+          <t>duplicate of p29 with different values</t>
         </is>
       </c>
     </row>
@@ -68856,23 +68899,23 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>duplicate of p30 with different values</t>
+          <t>duplicate of p29 with different values</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -68881,16 +68924,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>67.02.03</t>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>duplicate of p23 with different values</t>
+          <t>name mismatch vs nomenclator (37%): 'Ssuenn sa ae u u r ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
@@ -68906,16 +68949,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>74.02.05</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>duplicate of p23 with different values</t>
+          <t>duplicate of p30 with different values</t>
         </is>
       </c>
     </row>
@@ -68931,16 +68974,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>67.02.03.30</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>duplicate of p30 with different values</t>
         </is>
       </c>
     </row>
@@ -68956,16 +68999,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>67.02.05</t>
+          <t>74.02.06</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>duplicate of p30 with different values</t>
         </is>
       </c>
     </row>
@@ -68981,16 +69024,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>duplicate of p30 with different values</t>
         </is>
       </c>
     </row>
@@ -69006,16 +69049,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>duplicate of p24 with different values</t>
+          <t>duplicate of p31 with different values</t>
         </is>
       </c>
     </row>
@@ -69031,16 +69074,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>81.02.50</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>duplicate of p25 with different values</t>
+          <t>duplicate of p32 with different values</t>
         </is>
       </c>
     </row>
@@ -69056,16 +69099,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>68.02.15</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>duplicate of p26 with different values</t>
+          <t>duplicate of p32 with different values</t>
         </is>
       </c>
     </row>
@@ -69081,16 +69124,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>68.02.15.02</t>
+          <t>84.02.03</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>duplicate of p26 with different values</t>
+          <t>duplicate of p33 with different values</t>
         </is>
       </c>
     </row>
@@ -69106,16 +69149,16 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>84.02.03.02</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>duplicate of p26 with different values</t>
+          <t>duplicate of p33 with different values</t>
         </is>
       </c>
     </row>
@@ -69131,16 +69174,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>70.02.06</t>
+          <t>84.02.03.03</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>duplicate of p28 with different values</t>
+          <t>duplicate of p33 with different values</t>
         </is>
       </c>
     </row>
@@ -69156,23 +69199,23 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>duplicate of p28 with different values</t>
+          <t>duplicate of p34 with different values</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -69181,41 +69224,41 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>duplicate of p28 with different values</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20.05.30</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>duplicate of p29 with different values</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -69231,23 +69274,23 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>39.02.01</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>duplicate of p29 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -69256,23 +69299,23 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>55.01</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>duplicate of p29 with different values</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -69281,16 +69324,16 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>55.01.84</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Ssuenn sa ae u u r ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -69306,16 +69349,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>74.02.05</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>duplicate of p30 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -69331,16 +69374,16 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>74.02.05.01</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>duplicate of p30 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
@@ -69356,23 +69399,23 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>74.02.06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>duplicate of p30 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -69381,41 +69424,46 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>58.01</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>duplicate of p30 with different values</t>
+          <t>name mismatch vs nomenclator (40%): 'Pron uaa uoa  ne n e a)' vs 'Programe din Fondul European de Dezvolta'</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>duplicate of p31 with different values</t>
+          <t>65.02 total: parent 122.353.330,00 != sum(children) 7.335.100,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -69431,41 +69479,46 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>81.02.50</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>duplicate of p32 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>duplicate of p32 with different values</t>
+          <t>67.02 total: parent 6.391.080,00 != sum(children) 2.659.190,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -69481,16 +69534,16 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>84.02.03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>duplicate of p33 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -69506,73 +69559,83 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>84.02.03.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>duplicate of p33 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>84.02.03.03</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>duplicate of p33 with different values</t>
+          <t>70.02 total: parent 91.968.070,00 != sum(children) 22.810.190,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>duplicate of p34 with different values</t>
+          <t>70.02 credite_restante: parent 356.606,00 != sum(children) 48.475,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -69581,23 +69644,23 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -69606,16 +69669,21 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>74.02 total: parent 21.697.750,00 != sum(children) 1.002.500,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -69631,41 +69699,46 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>39.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>80.02</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>80.02 total: parent 4.991.010,00 != sum(children) 70.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -69681,41 +69754,46 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>81.02</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>81.02 total: parent 969.060,00 != sum(children) 950.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -69731,48 +69809,53 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>84.02 total: parent 116.827.600,00 != sum(children) 8.908.800,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -69781,16 +69864,16 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>58.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Pron uaa uoa  ne n e a)' vs 'Programe din Fondul European de Dezvolta'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -69806,7 +69889,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -69822,260 +69905,60 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>99.02</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>99.02 total: parent 2.600.000,00 != sum(children) 45.339.980,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>99.02</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>66</v>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>67</v>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>68</v>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>69</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>69</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>70</v>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>duplicate of p5 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>71</v>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>credite_restante</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
           <t>99.02 credite_restante: parent 0,00 != sum(children) 48.475,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>71</v>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>99.02 total: parent 2.600.000,00 != sum(children) 45.339.980,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -70090,7 +69973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -70112,7 +69995,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -70122,72 +70005,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1682</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1548</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>90.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>91.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>90.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>e8a8d15e4dbb221d7a8320b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2fc8ecbdc365901d2e7e338fc1241fdbe692363ad8f0c55a62d8878e70d9c6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 1)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-71, 1749 linii</t>
         </is>
